--- a/Tests/SwiftSheetsTests/Fixtures/interop/consumer-contract.xlsx
+++ b/Tests/SwiftSheetsTests/Fixtures/interop/consumer-contract.xlsx
@@ -195,14 +195,14 @@
   <futureMetadata name="XLDAPR" count="2">
     <bk>
       <extLst>
-        <ext uri="{BDBB8CDC-FA1E-496E-A857-3C3F30C029C3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
         </ext>
       </extLst>
     </bk>
     <bk>
       <extLst>
-        <ext uri="{BDBB8CDC-FA1E-496E-A857-3C3F30C029C3}">
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
           <xda:dynamicArrayProperties fDynamic="0" fCollapsed="0"/>
         </ext>
       </extLst>
